--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68.78</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>75.48999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>69.36</v>
+        <v>70.02</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>76.09</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>86.3</v>
+        <v>86.92</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>95.56999999999999</v>
+        <v>95.75</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>88.94</v>
+        <v>89.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>98.44</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>87.54000000000001</v>
+        <v>87.84</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>96.92</v>
+        <v>97.23</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>91.34999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>101.09</v>
+        <v>101.34</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>91.87</v>
+        <v>92.22</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>102.01</v>
+        <v>102.24</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.25</v>
+        <v>100.53</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>111.35</v>
+        <v>111.49</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.64</v>
+        <v>80.56</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>88.2</v>
+        <v>88.05</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>95.17</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.95</v>
+        <v>103.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Aug 2026</t>
+          <t>Data through: Sep 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5893,6 +5893,26 @@
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="F258" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5904,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10805,8 +10825,27 @@
         <v>76.94</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>35.79</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B257">
+  <conditionalFormatting sqref="B2:B258">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10818,7 +10857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C257">
+  <conditionalFormatting sqref="C2:C258">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10830,7 +10869,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D257">
+  <conditionalFormatting sqref="D2:D258">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10842,7 +10881,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E257">
+  <conditionalFormatting sqref="E2:E258">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>69.51000000000001</v>
+        <v>71.63</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>75.45</v>
+        <v>77.05</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>70.02</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>75.97</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>86.92</v>
+        <v>86.94</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>95.75</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>98.56</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>87.84</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>97.23</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>91.58</v>
+        <v>91.83</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>101.34</v>
+        <v>101.53</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>92.22</v>
+        <v>92.89</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>102.24</v>
+        <v>102.85</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.53</v>
+        <v>101.17</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>111.49</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.56</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>88.05</v>
+        <v>88.09</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.95999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.66</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Sep 2026</t>
+          <t>Data through: Oct 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5913,6 +5913,26 @@
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="C259" s="5" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="D259" s="5" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="E259" s="5" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="F259" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5924,7 +5944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10844,8 +10864,27 @@
         <v>35.79</v>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="C259" s="5" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="D259" s="5" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="E259" s="5" t="n">
+        <v>46.08</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B258">
+  <conditionalFormatting sqref="B2:B259">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10857,7 +10896,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C258">
+  <conditionalFormatting sqref="C2:C259">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10869,7 +10908,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D258">
+  <conditionalFormatting sqref="D2:D259">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10881,7 +10920,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E258">
+  <conditionalFormatting sqref="E2:E259">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
